--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/moscow_special_modifiers.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/Abilities/Specials/moscow_special_modifiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\Abilities\Specials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110C3554-F9E6-41D8-9F27-B7D73DC3DAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E2B558-43E6-4DFD-B2FC-96B09D633630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="2025" windowWidth="19395" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="modifiers" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -42,79 +42,83 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Flat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player/Weapon/Spell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tree Type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PercentMul</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PercentAdd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구 개수 +3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구 개수 x2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구 크기 x1.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 20%p 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구 충돌 데미지 x1.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExplosionDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구 폭발 데미지 x1.2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MovementSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootingBurstCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>BurstCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player/Weapon/Spell</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tree Type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weapon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PercentMul</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Speed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PercentAdd</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spell</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염구 개수 +3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염구 개수 x2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염구 크기 x1.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 20%p 증가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염구 충돌 데미지 x1.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExplosionDamage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염구 폭발 데미지 x1.2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -450,10 +454,10 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -477,19 +481,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>0.2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1"/>
     </row>
@@ -501,19 +505,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1"/>
     </row>
@@ -525,19 +529,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -548,19 +552,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>0.2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -571,19 +575,19 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>0.2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -594,19 +598,19 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>0.2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -617,19 +621,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>0.2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
